--- a/data/trans_orig/P3A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2007</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88157</t>
+          <t>88710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121004</t>
+          <t>121924</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>203973</t>
+          <t>203968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228219</t>
+          <t>228161</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>297900</t>
+          <t>298938</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>344539</t>
+          <t>344410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>152006</t>
+          <t>151086</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184853</t>
+          <t>184300</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31605</t>
+          <t>31663</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55851</t>
+          <t>55856</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188295</t>
+          <t>188424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>234934</t>
+          <t>233896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>165852</t>
+          <t>165735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>209645</t>
+          <t>210854</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>402063</t>
+          <t>405116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>435720</t>
+          <t>436712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>577685</t>
+          <t>575021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>637977</t>
+          <t>641642</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>283430</t>
+          <t>282221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327223</t>
+          <t>327340</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68229</t>
+          <t>67237</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101886</t>
+          <t>98833</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>359047</t>
+          <t>355382</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>419339</t>
+          <t>422003</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75724</t>
+          <t>75989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109032</t>
+          <t>107839</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>265951</t>
+          <t>264740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>292478</t>
+          <t>291772</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>345312</t>
+          <t>343511</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>394845</t>
+          <t>393732</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>209814</t>
+          <t>211007</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>243122</t>
+          <t>242857</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42934</t>
+          <t>43640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69461</t>
+          <t>70672</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>259413</t>
+          <t>260526</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>308946</t>
+          <t>310747</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92636</t>
+          <t>90842</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127169</t>
+          <t>127360</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>288580</t>
+          <t>288633</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>317330</t>
+          <t>318597</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,93%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>388367</t>
+          <t>387688</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>437937</t>
+          <t>441154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>60,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231502</t>
+          <t>231311</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266035</t>
+          <t>267829</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52973</t>
+          <t>51706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81723</t>
+          <t>81670</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>291037</t>
+          <t>287820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340607</t>
+          <t>341286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,82%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60203</t>
+          <t>59957</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87794</t>
+          <t>87974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>169042</t>
+          <t>169520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188736</t>
+          <t>188585</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>234102</t>
+          <t>235236</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>274160</t>
+          <t>273386</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115514</t>
+          <t>115334</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143105</t>
+          <t>143351</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18932</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38626</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136816</t>
+          <t>137590</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>176874</t>
+          <t>175740</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,76%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58303</t>
+          <t>59244</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>87611</t>
+          <t>88462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>231070</t>
+          <t>231006</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>254432</t>
+          <t>253765</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>292504</t>
+          <t>292495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>338141</t>
+          <t>338093</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183200</t>
+          <t>182349</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>212508</t>
+          <t>211567</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23712</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47074</t>
+          <t>47138</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>210814</t>
+          <t>210862</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>256451</t>
+          <t>256460</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>225919</t>
+          <t>224878</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>276405</t>
+          <t>274426</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>530955</t>
+          <t>532068</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>564385</t>
+          <t>564983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>767200</t>
+          <t>765742</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>831208</t>
+          <t>833868</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,66%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>338622</t>
+          <t>340601</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>389108</t>
+          <t>390149</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>71450</t>
+          <t>70852</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>104880</t>
+          <t>103767</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>419654</t>
+          <t>416994</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>483662</t>
+          <t>485120</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>204340</t>
+          <t>204202</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>257105</t>
+          <t>258484</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>619287</t>
+          <t>618632</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>663653</t>
+          <t>661390</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>832590</t>
+          <t>832044</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>909019</t>
+          <t>909991</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,62%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>485808</t>
+          <t>484429</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>538573</t>
+          <t>538711</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119858</t>
+          <t>122121</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>164224</t>
+          <t>164879</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>617405</t>
+          <t>616433</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>693834</t>
+          <t>694380</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1063343</t>
+          <t>1064943</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1174164</t>
+          <t>1177799</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2789690</t>
+          <t>2791090</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2877311</t>
+          <t>2877241</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3881039</t>
+          <t>3878149</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4032335</t>
+          <t>4043597</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,8%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2101497</t>
+          <t>2097862</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2212318</t>
+          <t>2210718</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>497334</t>
+          <t>497404</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>584955</t>
+          <t>583555</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2617972</t>
+          <t>2606710</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2769268</t>
+          <t>2772158</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,68%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2012</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119209</t>
+          <t>119673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>156365</t>
+          <t>154966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>238305</t>
+          <t>237347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>260164</t>
+          <t>260528</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>362638</t>
+          <t>364556</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>409922</t>
+          <t>410673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138373</t>
+          <t>139772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175529</t>
+          <t>175065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27081</t>
+          <t>26717</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48940</t>
+          <t>49898</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172061</t>
+          <t>171310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>219345</t>
+          <t>217427</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,36%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168837</t>
+          <t>169157</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>211912</t>
+          <t>210732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>419850</t>
+          <t>419933</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>454936</t>
+          <t>456415</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>592042</t>
+          <t>598672</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>659480</t>
+          <t>663053</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,48%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>292556</t>
+          <t>293736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335631</t>
+          <t>335311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68829</t>
+          <t>67350</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103915</t>
+          <t>103832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>368753</t>
+          <t>365180</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>436191</t>
+          <t>429561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117337</t>
+          <t>117293</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155008</t>
+          <t>151427</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>271473</t>
+          <t>271863</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>299498</t>
+          <t>298588</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>391971</t>
+          <t>394989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>443275</t>
+          <t>447831</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>169038</t>
+          <t>172619</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206709</t>
+          <t>206753</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41522</t>
+          <t>42432</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69547</t>
+          <t>69157</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>221791</t>
+          <t>217235</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273095</t>
+          <t>270077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160542</t>
+          <t>162551</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202576</t>
+          <t>202510</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>307869</t>
+          <t>308387</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>337789</t>
+          <t>338586</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>481228</t>
+          <t>479846</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>535745</t>
+          <t>534137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>70,01%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171406</t>
+          <t>171472</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>213440</t>
+          <t>211431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51162</t>
+          <t>50365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81082</t>
+          <t>80564</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227188</t>
+          <t>228796</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>281705</t>
+          <t>283087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51498</t>
+          <t>51241</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>78714</t>
+          <t>79064</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163499</t>
+          <t>163675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187131</t>
+          <t>186554</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220290</t>
+          <t>218965</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>262055</t>
+          <t>260935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>60,37%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>133904</t>
+          <t>133554</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161120</t>
+          <t>161377</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>32460</t>
+          <t>33037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>56092</t>
+          <t>55916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>170154</t>
+          <t>171274</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>211919</t>
+          <t>213244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,34%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>102733</t>
+          <t>101710</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>136630</t>
+          <t>136001</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>227977</t>
+          <t>229401</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>251598</t>
+          <t>252000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>337431</t>
+          <t>337398</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>381960</t>
+          <t>384177</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137351</t>
+          <t>137980</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>171248</t>
+          <t>172271</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28433</t>
+          <t>28031</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52054</t>
+          <t>50630</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>172052</t>
+          <t>169835</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216581</t>
+          <t>216614</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>273224</t>
+          <t>277016</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>330177</t>
+          <t>333735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>549962</t>
+          <t>549614</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>589238</t>
+          <t>593526</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>835613</t>
+          <t>833487</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>911676</t>
+          <t>909502</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>67,04%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>332611</t>
+          <t>329053</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>389564</t>
+          <t>385772</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104615</t>
+          <t>100327</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>143891</t>
+          <t>144239</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>444965</t>
+          <t>447139</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>521028</t>
+          <t>523154</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>338261</t>
+          <t>335549</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>394384</t>
+          <t>394881</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>657836</t>
+          <t>658084</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>702619</t>
+          <t>701322</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1004805</t>
+          <t>1001669</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1087120</t>
+          <t>1087628</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,94%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>384714</t>
+          <t>384217</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>440837</t>
+          <t>443549</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119233</t>
+          <t>120530</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>164016</t>
+          <t>163768</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>513830</t>
+          <t>513322</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>596145</t>
+          <t>599281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,43%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1433624</t>
+          <t>1437310</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1559438</t>
+          <t>1559799</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2921499</t>
+          <t>2926098</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3015622</t>
+          <t>3019903</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4384190</t>
+          <t>4386140</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4552911</t>
+          <t>4552176</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1866281</t>
+          <t>1865920</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1992095</t>
+          <t>1988409</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>540686</t>
+          <t>536405</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>634809</t>
+          <t>630210</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2429116</t>
+          <t>2429851</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2597837</t>
+          <t>2595887</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,18%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2016</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132851</t>
+          <t>134189</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169008</t>
+          <t>169319</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,22%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>246135</t>
+          <t>245393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>267806</t>
+          <t>267531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>385159</t>
+          <t>385562</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>430825</t>
+          <t>432174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124753</t>
+          <t>124442</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>160910</t>
+          <t>159572</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20897</t>
+          <t>21172</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>42568</t>
+          <t>43310</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>151639</t>
+          <t>150290</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197305</t>
+          <t>196902</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>212511</t>
+          <t>213820</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>259170</t>
+          <t>259980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,95%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>431649</t>
+          <t>430915</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>465315</t>
+          <t>464124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>656882</t>
+          <t>651498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>717158</t>
+          <t>712384</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,77%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>239689</t>
+          <t>238879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>286348</t>
+          <t>285039</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56835</t>
+          <t>58026</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90501</t>
+          <t>91235</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>303851</t>
+          <t>308625</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>364127</t>
+          <t>369511</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171496</t>
+          <t>170705</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>205779</t>
+          <t>203458</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>291185</t>
+          <t>290298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>311410</t>
+          <t>312225</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>468974</t>
+          <t>469817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>511545</t>
+          <t>511374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>112050</t>
+          <t>114371</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146333</t>
+          <t>147124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45124</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142593</t>
+          <t>142764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185164</t>
+          <t>184321</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171201</t>
+          <t>171107</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211441</t>
+          <t>209321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,45%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>303722</t>
+          <t>304871</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>335344</t>
+          <t>335372</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>486437</t>
+          <t>486582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>537429</t>
+          <t>536939</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>156619</t>
+          <t>158739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196859</t>
+          <t>196953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,55%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51939</t>
+          <t>51911</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83561</t>
+          <t>82412</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217914</t>
+          <t>218404</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268906</t>
+          <t>268761</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106873</t>
+          <t>107188</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>135172</t>
+          <t>136300</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>194078</t>
+          <t>192972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>208534</t>
+          <t>208648</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>304895</t>
+          <t>306570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>341406</t>
+          <t>340528</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,1%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76049</t>
+          <t>74921</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104348</t>
+          <t>104033</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>8985</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23555</t>
+          <t>24661</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>87448</t>
+          <t>88326</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123959</t>
+          <t>122284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,51%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>98608</t>
+          <t>99018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132190</t>
+          <t>131297</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>226111</t>
+          <t>225661</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>250295</t>
+          <t>249212</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>331952</t>
+          <t>331720</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>375630</t>
+          <t>376250</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>70,52%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129299</t>
+          <t>130192</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162881</t>
+          <t>162471</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>22862</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45963</t>
+          <t>46413</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>157933</t>
+          <t>157313</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>201611</t>
+          <t>201843</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,83%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>317938</t>
+          <t>315510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>370827</t>
+          <t>370261</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>580673</t>
+          <t>580253</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>617230</t>
+          <t>615174</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>909392</t>
+          <t>907922</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>979880</t>
+          <t>977889</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,72%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>284681</t>
+          <t>285247</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>337570</t>
+          <t>339998</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72032</t>
+          <t>74088</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>108589</t>
+          <t>109009</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>364890</t>
+          <t>366881</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>435378</t>
+          <t>436848</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>424476</t>
+          <t>426311</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>478805</t>
+          <t>484187</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>703301</t>
+          <t>699215</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>741316</t>
+          <t>739828</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1139338</t>
+          <t>1137210</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1209627</t>
+          <t>1210880</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,46%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>299778</t>
+          <t>294396</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>354107</t>
+          <t>352272</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>84851</t>
+          <t>86339</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>122866</t>
+          <t>126952</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>395123</t>
+          <t>393870</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>465412</t>
+          <t>467540</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1739920</t>
+          <t>1734100</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1853938</t>
+          <t>1856067</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3055840</t>
+          <t>3051482</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3134887</t>
+          <t>3135285</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4810233</t>
+          <t>4816483</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4968766</t>
+          <t>4963963</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1531371</t>
+          <t>1529242</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1645389</t>
+          <t>1651209</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>404693</t>
+          <t>404295</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>483740</t>
+          <t>488098</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1956124</t>
+          <t>1960927</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2114657</t>
+          <t>2108407</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,45%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente el/la entrevistado/a en 2023</t>
+          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>166300</t>
+          <t>167074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>206399</t>
+          <t>206429</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>248852</t>
+          <t>249691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273352</t>
+          <t>273876</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>426128</t>
+          <t>427060</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>474080</t>
+          <t>474473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105044</t>
+          <t>105014</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145143</t>
+          <t>144369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16283</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40783</t>
+          <t>39944</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126997</t>
+          <t>126604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174949</t>
+          <t>174017</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>347079</t>
+          <t>346819</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>403807</t>
+          <t>401491</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>453998</t>
+          <t>455200</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>482940</t>
+          <t>483614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>812425</t>
+          <t>812061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>875669</t>
+          <t>877282</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,9%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114583</t>
+          <t>116899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171311</t>
+          <t>171571</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32029</t>
+          <t>31355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>60971</t>
+          <t>59769</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>157690</t>
+          <t>156077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>220934</t>
+          <t>221298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>226839</t>
+          <t>227949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>256939</t>
+          <t>255290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>299787</t>
+          <t>300583</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>319515</t>
+          <t>320661</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>535459</t>
+          <t>534332</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>570056</t>
+          <t>569993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58479</t>
+          <t>60128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88579</t>
+          <t>87469</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28353</t>
+          <t>27207</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48081</t>
+          <t>47285</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93230</t>
+          <t>93293</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127827</t>
+          <t>128954</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,44%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>177915</t>
+          <t>179981</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223868</t>
+          <t>223721</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>411274</t>
+          <t>409158</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>450102</t>
+          <t>449595</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>592483</t>
+          <t>598681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>678792</t>
+          <t>675463</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,69%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88689</t>
+          <t>88836</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134642</t>
+          <t>132576</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25616</t>
+          <t>26123</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64444</t>
+          <t>66560</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>109482</t>
+          <t>112811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>195791</t>
+          <t>189593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148317</t>
+          <t>149298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>164061</t>
+          <t>163448</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>239133</t>
+          <t>238500</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>253393</t>
+          <t>253181</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>393720</t>
+          <t>392750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>416463</t>
+          <t>416839</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14214</t>
+          <t>14827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29958</t>
+          <t>28977</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>20279</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20592</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43335</t>
+          <t>44305</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>193814</t>
+          <t>193669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>220748</t>
+          <t>219858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>227944</t>
+          <t>228734</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>240866</t>
+          <t>241805</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>427778</t>
+          <t>428595</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>457300</t>
+          <t>457375</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>48888</t>
+          <t>49778</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75822</t>
+          <t>75967</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>16190</t>
+          <t>15251</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29112</t>
+          <t>28322</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69392</t>
+          <t>69317</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98914</t>
+          <t>98097</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>423462</t>
+          <t>426531</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>478257</t>
+          <t>480536</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>734978</t>
+          <t>735039</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>812568</t>
+          <t>813207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1167712</t>
+          <t>1164053</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1314159</t>
+          <t>1315381</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,27%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>146022</t>
+          <t>143743</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200817</t>
+          <t>197748</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36697</t>
+          <t>36058</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>114287</t>
+          <t>114226</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>159385</t>
+          <t>158163</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>305832</t>
+          <t>309491</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>127098</t>
+          <t>132880</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>413387</t>
+          <t>414247</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>651951</t>
+          <t>651164</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>678805</t>
+          <t>679863</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>605873</t>
+          <t>596991</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1143303</t>
+          <t>1143817</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>515333</t>
+          <t>514473</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>801622</t>
+          <t>795840</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>38926</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>65780</t>
+          <t>66567</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>503149</t>
+          <t>502635</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1040579</t>
+          <t>1049461</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1645467</t>
+          <t>1616269</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2299797</t>
+          <t>2302431</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3352739</t>
+          <t>3353826</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3457073</t>
+          <t>3455773</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4804174</t>
+          <t>4883769</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5760368</t>
+          <t>5758566</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1158921</t>
+          <t>1156287</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1813251</t>
+          <t>1842449</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>253947</t>
+          <t>255247</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>358281</t>
+          <t>357194</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1409370</t>
+          <t>1411172</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2365564</t>
+          <t>2285969</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P3A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88710</t>
+          <t>88095</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>121924</t>
+          <t>120554</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>203968</t>
+          <t>203578</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228161</t>
+          <t>228211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>298938</t>
+          <t>297710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>344410</t>
+          <t>344470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,65%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>151086</t>
+          <t>152456</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>184300</t>
+          <t>184915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31663</t>
+          <t>31613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55856</t>
+          <t>56246</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>188424</t>
+          <t>188364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>233896</t>
+          <t>235124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>165735</t>
+          <t>167283</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>210854</t>
+          <t>212371</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>405116</t>
+          <t>404624</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>436712</t>
+          <t>437175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>575021</t>
+          <t>579632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>641642</t>
+          <t>638143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282221</t>
+          <t>280704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327340</t>
+          <t>325792</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67237</t>
+          <t>66774</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>98833</t>
+          <t>99325</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>355382</t>
+          <t>358881</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>422003</t>
+          <t>417392</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,86%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>75989</t>
+          <t>75904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>107839</t>
+          <t>110208</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>264740</t>
+          <t>264653</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>291772</t>
+          <t>291601</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>343511</t>
+          <t>343051</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>393732</t>
+          <t>393897</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>211007</t>
+          <t>208638</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>242857</t>
+          <t>242942</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43640</t>
+          <t>43811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>70672</t>
+          <t>70759</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>260526</t>
+          <t>260361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>310747</t>
+          <t>311207</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90842</t>
+          <t>91253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>127360</t>
+          <t>127094</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>288633</t>
+          <t>290940</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>318597</t>
+          <t>317114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>387688</t>
+          <t>388011</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>441154</t>
+          <t>442024</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,64%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231311</t>
+          <t>231577</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>267829</t>
+          <t>267418</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>64,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51706</t>
+          <t>53189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81670</t>
+          <t>79363</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>287820</t>
+          <t>286950</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341286</t>
+          <t>340963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59957</t>
+          <t>58439</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87974</t>
+          <t>86750</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>169520</t>
+          <t>169188</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188585</t>
+          <t>188378</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235236</t>
+          <t>233654</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273386</t>
+          <t>274628</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,82%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115334</t>
+          <t>116558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143351</t>
+          <t>144869</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19083</t>
+          <t>19290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38480</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137590</t>
+          <t>136348</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>175740</t>
+          <t>177322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,15%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59244</t>
+          <t>59211</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>88462</t>
+          <t>88866</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>231006</t>
+          <t>230617</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>253765</t>
+          <t>253073</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>292495</t>
+          <t>291295</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>338093</t>
+          <t>338655</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182349</t>
+          <t>181945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>211567</t>
+          <t>211600</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24379</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47138</t>
+          <t>47527</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>210862</t>
+          <t>210300</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>256460</t>
+          <t>257660</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,94%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>224878</t>
+          <t>227270</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>274426</t>
+          <t>276481</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>532068</t>
+          <t>532117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>564983</t>
+          <t>563545</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>765742</t>
+          <t>768327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>833868</t>
+          <t>833691</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,22%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,65%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>340601</t>
+          <t>338546</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>390149</t>
+          <t>387757</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70852</t>
+          <t>72290</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>103767</t>
+          <t>103718</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>416994</t>
+          <t>417171</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>485120</t>
+          <t>482535</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>204202</t>
+          <t>204583</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>258484</t>
+          <t>256058</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>618632</t>
+          <t>618867</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>661390</t>
+          <t>661230</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>832044</t>
+          <t>828681</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>909991</t>
+          <t>907526</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,45%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>484429</t>
+          <t>486855</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>538711</t>
+          <t>538330</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,21%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>122121</t>
+          <t>122281</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>164879</t>
+          <t>164644</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>616433</t>
+          <t>618898</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>694380</t>
+          <t>697743</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,71%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1064943</t>
+          <t>1064692</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1177799</t>
+          <t>1178098</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2791090</t>
+          <t>2796494</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2877241</t>
+          <t>2881418</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3878149</t>
+          <t>3879112</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4043597</t>
+          <t>4037308</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,71%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2097862</t>
+          <t>2097563</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2210718</t>
+          <t>2210969</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>497404</t>
+          <t>493227</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>583555</t>
+          <t>578151</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2606710</t>
+          <t>2612999</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2772158</t>
+          <t>2771195</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,67%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119673</t>
+          <t>117689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154966</t>
+          <t>153959</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>237347</t>
+          <t>236410</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>260528</t>
+          <t>260575</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>364556</t>
+          <t>362281</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>410673</t>
+          <t>408550</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,2%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139772</t>
+          <t>140779</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175065</t>
+          <t>177049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26717</t>
+          <t>26670</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49898</t>
+          <t>50835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171310</t>
+          <t>173433</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217427</t>
+          <t>219702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>169157</t>
+          <t>168039</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>210732</t>
+          <t>213461</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>419933</t>
+          <t>419645</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>456415</t>
+          <t>454839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>598672</t>
+          <t>591206</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>663053</t>
+          <t>659402</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,13%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>293736</t>
+          <t>291007</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335311</t>
+          <t>336429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67350</t>
+          <t>68926</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103832</t>
+          <t>104120</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>365180</t>
+          <t>368831</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>429561</t>
+          <t>437027</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117293</t>
+          <t>117509</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>151427</t>
+          <t>151982</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>271863</t>
+          <t>271319</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>298588</t>
+          <t>298159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>394989</t>
+          <t>393865</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>447831</t>
+          <t>443833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172619</t>
+          <t>172064</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>206753</t>
+          <t>206537</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42432</t>
+          <t>42861</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69157</t>
+          <t>69701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>217235</t>
+          <t>221233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>270077</t>
+          <t>271201</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,78%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162551</t>
+          <t>162375</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202510</t>
+          <t>201539</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>308387</t>
+          <t>308584</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>338586</t>
+          <t>338642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>479846</t>
+          <t>480565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>534137</t>
+          <t>531232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171472</t>
+          <t>172443</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>211431</t>
+          <t>211607</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50365</t>
+          <t>50309</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80564</t>
+          <t>80367</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>228796</t>
+          <t>231701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>283087</t>
+          <t>282368</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51241</t>
+          <t>52526</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79064</t>
+          <t>80015</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>163675</t>
+          <t>164342</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>186554</t>
+          <t>187327</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>218965</t>
+          <t>219718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>260935</t>
+          <t>262715</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,78%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>133554</t>
+          <t>132603</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>161377</t>
+          <t>160092</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33037</t>
+          <t>32264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55916</t>
+          <t>55249</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>171274</t>
+          <t>169494</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>213244</t>
+          <t>212491</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,16%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>101710</t>
+          <t>104284</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>136001</t>
+          <t>137195</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>229401</t>
+          <t>229104</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>252000</t>
+          <t>251627</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>337398</t>
+          <t>337020</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>384177</t>
+          <t>384314</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,37%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>137980</t>
+          <t>136786</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>172271</t>
+          <t>169697</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28031</t>
+          <t>28404</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50630</t>
+          <t>50927</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>169835</t>
+          <t>169698</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>216614</t>
+          <t>216992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>277016</t>
+          <t>279318</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>333735</t>
+          <t>329710</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>549614</t>
+          <t>550821</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>593526</t>
+          <t>592445</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>833487</t>
+          <t>835928</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>909502</t>
+          <t>910900</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,14%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>329053</t>
+          <t>333078</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>385772</t>
+          <t>383470</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100327</t>
+          <t>101408</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>144239</t>
+          <t>143032</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>447139</t>
+          <t>445741</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>523154</t>
+          <t>520713</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>335549</t>
+          <t>332344</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>394881</t>
+          <t>392438</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>658084</t>
+          <t>657559</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>701322</t>
+          <t>703135</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1001669</t>
+          <t>1008253</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1087628</t>
+          <t>1085134</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,78%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>384217</t>
+          <t>386660</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>443549</t>
+          <t>446754</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>120530</t>
+          <t>118717</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>163768</t>
+          <t>164293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>513322</t>
+          <t>515816</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>599281</t>
+          <t>592697</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1437310</t>
+          <t>1437562</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1559799</t>
+          <t>1557613</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2926098</t>
+          <t>2923419</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3019903</t>
+          <t>3017987</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4386140</t>
+          <t>4385240</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4552176</t>
+          <t>4552131</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1865920</t>
+          <t>1868106</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1988409</t>
+          <t>1988157</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>536405</t>
+          <t>538321</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>630210</t>
+          <t>632889</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2429851</t>
+          <t>2429896</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2595887</t>
+          <t>2596787</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>134189</t>
+          <t>132422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>169319</t>
+          <t>167308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>56,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>245393</t>
+          <t>246261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>267531</t>
+          <t>269239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>385562</t>
+          <t>387611</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>432174</t>
+          <t>430516</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,91%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124442</t>
+          <t>126453</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159572</t>
+          <t>161339</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21172</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>43310</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>150290</t>
+          <t>151948</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196902</t>
+          <t>194853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>213820</t>
+          <t>214137</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>259980</t>
+          <t>258659</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>42,86%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,11%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>430915</t>
+          <t>432639</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>464124</t>
+          <t>465467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>651498</t>
+          <t>652069</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>712384</t>
+          <t>715106</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>70,04%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>238879</t>
+          <t>240200</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>285039</t>
+          <t>284722</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58026</t>
+          <t>56683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91235</t>
+          <t>89511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>308625</t>
+          <t>305903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>369511</t>
+          <t>368940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170705</t>
+          <t>170168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203458</t>
+          <t>204025</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>290298</t>
+          <t>289913</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>312225</t>
+          <t>311951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>469817</t>
+          <t>467917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>511374</t>
+          <t>509988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,82%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,96%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114371</t>
+          <t>113804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147124</t>
+          <t>147661</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>24358</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>46396</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>142764</t>
+          <t>144150</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184321</t>
+          <t>186221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>171107</t>
+          <t>171494</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>209321</t>
+          <t>210734</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>304871</t>
+          <t>304627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>335372</t>
+          <t>336154</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>486582</t>
+          <t>485024</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>536939</t>
+          <t>536059</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>70,97%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158739</t>
+          <t>157326</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>196953</t>
+          <t>196566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51911</t>
+          <t>51129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82412</t>
+          <t>82656</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218404</t>
+          <t>219284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268761</t>
+          <t>270319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107188</t>
+          <t>106604</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136300</t>
+          <t>134875</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>192972</t>
+          <t>193776</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>208648</t>
+          <t>208904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>306570</t>
+          <t>307699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>340528</t>
+          <t>342238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,8%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74921</t>
+          <t>76346</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104033</t>
+          <t>104617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8985</t>
+          <t>8729</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24661</t>
+          <t>23857</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>88326</t>
+          <t>86616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122284</t>
+          <t>121155</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99018</t>
+          <t>99652</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>131297</t>
+          <t>130620</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>225661</t>
+          <t>225832</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>249212</t>
+          <t>249181</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>331720</t>
+          <t>330588</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>376250</t>
+          <t>374424</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130192</t>
+          <t>130869</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>162471</t>
+          <t>161837</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22862</t>
+          <t>22893</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46413</t>
+          <t>46242</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>157313</t>
+          <t>159139</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>201843</t>
+          <t>202975</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,04%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>315510</t>
+          <t>318723</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>370261</t>
+          <t>371831</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>580253</t>
+          <t>578368</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>615174</t>
+          <t>616318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>907922</t>
+          <t>911405</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>977889</t>
+          <t>979057</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>285247</t>
+          <t>283677</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>339998</t>
+          <t>336785</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>74088</t>
+          <t>72944</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>109009</t>
+          <t>110894</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>366881</t>
+          <t>365713</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>436848</t>
+          <t>433365</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>426311</t>
+          <t>427114</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>484187</t>
+          <t>481842</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>699215</t>
+          <t>700486</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>739828</t>
+          <t>739088</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1137210</t>
+          <t>1138641</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1210880</t>
+          <t>1209670</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,38%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>294396</t>
+          <t>296741</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>352272</t>
+          <t>351469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>86339</t>
+          <t>87079</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>126952</t>
+          <t>125681</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>393870</t>
+          <t>395080</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>467540</t>
+          <t>466109</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1734100</t>
+          <t>1732899</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1856067</t>
+          <t>1853887</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3051482</t>
+          <t>3055023</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3135285</t>
+          <t>3134357</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4816483</t>
+          <t>4818389</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4963963</t>
+          <t>4971138</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,79%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1529242</t>
+          <t>1531422</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1651209</t>
+          <t>1652410</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>404295</t>
+          <t>405223</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>488098</t>
+          <t>484557</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1960927</t>
+          <t>1953752</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2108407</t>
+          <t>2106501</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>186588</t>
+          <t>183501</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>167074</t>
+          <t>165114</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>206429</t>
+          <t>201308</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>264925</t>
+          <t>290022</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>249691</t>
+          <t>277295</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273876</t>
+          <t>298652</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>451513</t>
+          <t>473523</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>427060</t>
+          <t>449896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>474473</t>
+          <t>493567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>124855</t>
+          <t>135344</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105014</t>
+          <t>117537</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144369</t>
+          <t>153731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>26039</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>17409</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39944</t>
+          <t>38766</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>149564</t>
+          <t>161383</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126604</t>
+          <t>141339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174017</t>
+          <t>185010</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>375996</t>
+          <t>388911</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>346819</t>
+          <t>361875</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>401491</t>
+          <t>414307</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>471212</t>
+          <t>497943</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>455200</t>
+          <t>479610</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>483614</t>
+          <t>511814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>847208</t>
+          <t>886854</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>812061</t>
+          <t>852899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>877282</t>
+          <t>915286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,97%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>142394</t>
+          <t>141736</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>116899</t>
+          <t>116340</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171571</t>
+          <t>168772</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>43757</t>
+          <t>48551</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31355</t>
+          <t>34680</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59769</t>
+          <t>66884</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>186151</t>
+          <t>190287</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156077</t>
+          <t>161855</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221298</t>
+          <t>224242</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>242148</t>
+          <t>240290</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>227949</t>
+          <t>225113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>255290</t>
+          <t>252900</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>311471</t>
+          <t>318735</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>300583</t>
+          <t>308112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>320661</t>
+          <t>327186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,27 +11453,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>553619</t>
+          <t>559025</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>534332</t>
+          <t>540830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>569993</t>
+          <t>576194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>73270</t>
+          <t>75094</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60128</t>
+          <t>62484</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87469</t>
+          <t>90271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36397</t>
+          <t>36401</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27207</t>
+          <t>27950</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47285</t>
+          <t>47024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,22 +11566,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>109667</t>
+          <t>111495</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93293</t>
+          <t>94326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>128954</t>
+          <t>129690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315418</t>
+          <t>315384</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>347868</t>
+          <t>355136</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>347868</t>
+          <t>355136</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>347868</t>
+          <t>355136</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>670520</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>670520</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>670520</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>202930</t>
+          <t>240911</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>179981</t>
+          <t>214471</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223721</t>
+          <t>265382</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>430401</t>
+          <t>372803</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>409158</t>
+          <t>353270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>449595</t>
+          <t>386126</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>633330</t>
+          <t>613715</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>598681</t>
+          <t>581237</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>675463</t>
+          <t>643085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>109627</t>
+          <t>132234</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88836</t>
+          <t>107763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>132576</t>
+          <t>158674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>45317</t>
+          <t>49158</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26123</t>
+          <t>35835</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66560</t>
+          <t>68691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>154944</t>
+          <t>181392</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>112811</t>
+          <t>152022</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>189593</t>
+          <t>213870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>26,9%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>157093</t>
+          <t>180895</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>149298</t>
+          <t>171601</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163448</t>
+          <t>187858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>247405</t>
+          <t>216270</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>238500</t>
+          <t>207422</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>253181</t>
+          <t>221388</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>404498</t>
+          <t>397164</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>392750</t>
+          <t>384815</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>416839</t>
+          <t>407013</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21182</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28977</t>
+          <t>33580</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11374</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5598</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20279</t>
+          <t>21496</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>32557</t>
+          <t>36935</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20216</t>
+          <t>27086</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44305</t>
+          <t>49284</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>205181</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>205181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178275</t>
+          <t>205181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437055</t>
+          <t>434099</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437055</t>
+          <t>434099</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437055</t>
+          <t>434099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>207574</t>
+          <t>209402</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>193669</t>
+          <t>196326</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>219858</t>
+          <t>220581</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>235819</t>
+          <t>242112</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>228734</t>
+          <t>235011</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>241805</t>
+          <t>247694</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>443393</t>
+          <t>451515</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>428595</t>
+          <t>435028</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>457375</t>
+          <t>463444</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>62062</t>
+          <t>61305</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49778</t>
+          <t>50126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75967</t>
+          <t>74381</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>21237</t>
+          <t>21638</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15251</t>
+          <t>16056</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>28739</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>83299</t>
+          <t>82942</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>69317</t>
+          <t>71013</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98097</t>
+          <t>99429</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>452810</t>
+          <t>522928</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>426531</t>
+          <t>491654</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>480536</t>
+          <t>550133</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>769182</t>
+          <t>677877</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>735039</t>
+          <t>655192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>813207</t>
+          <t>695503</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1221992</t>
+          <t>1200804</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1164053</t>
+          <t>1160707</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1315381</t>
+          <t>1231060</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>82,52%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>171469</t>
+          <t>196759</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>143743</t>
+          <t>169554</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>197748</t>
+          <t>228033</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>80083</t>
+          <t>94180</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36058</t>
+          <t>76554</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>114226</t>
+          <t>116865</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>251552</t>
+          <t>290940</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>158163</t>
+          <t>260684</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>309491</t>
+          <t>331037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>295470</t>
+          <t>345719</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>132880</t>
+          <t>318914</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>414247</t>
+          <t>377711</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>667162</t>
+          <t>770160</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>651164</t>
+          <t>751254</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>679863</t>
+          <t>785598</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>962632</t>
+          <t>1115880</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>596991</t>
+          <t>1076302</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1143817</t>
+          <t>1154283</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>633250</t>
+          <t>452353</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>514473</t>
+          <t>420361</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>795840</t>
+          <t>479158</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>50569</t>
+          <t>61171</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37868</t>
+          <t>45733</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66567</t>
+          <t>80077</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>683820</t>
+          <t>513523</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>502635</t>
+          <t>475120</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1049461</t>
+          <t>553101</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2120608</t>
+          <t>2312557</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1616269</t>
+          <t>2251481</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2302431</t>
+          <t>2374350</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3397577</t>
+          <t>3385923</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3353826</t>
+          <t>3345644</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3455773</t>
+          <t>3421280</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>5518185</t>
+          <t>5698481</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4883769</t>
+          <t>5618246</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5758566</t>
+          <t>5775071</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,47%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1338110</t>
+          <t>1219112</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1156287</t>
+          <t>1157319</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1842449</t>
+          <t>1280188</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>313443</t>
+          <t>349786</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>255247</t>
+          <t>314429</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>357194</t>
+          <t>390065</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1651553</t>
+          <t>1568897</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1411172</t>
+          <t>1492307</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2285969</t>
+          <t>1649132</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458718</t>
+          <t>3531669</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3711020</t>
+          <t>3735709</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7169738</t>
+          <t>7267378</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">

--- a/data/trans_orig/P3A_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P3A_R-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2007 (tasa de respuesta: 99,92%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2012 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2016 (tasa de respuesta: 99,8%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2016 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si las tareas domésticas las realiza principalmente la persona entrevistada en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Población según si las tareas domésticas las realiza principalmente la persona entrevistada [En 2023 se ha construido a partir de la pregunta multirrespuesta] en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
